--- a/output/Results - sem4.xlsx
+++ b/output/Results - sem4.xlsx
@@ -133,6 +133,9 @@
     <t>230544</t>
   </si>
   <si>
+    <t>230121</t>
+  </si>
+  <si>
     <t>230355</t>
   </si>
   <si>
@@ -154,6 +157,9 @@
     <t>230108</t>
   </si>
   <si>
+    <t>230100</t>
+  </si>
+  <si>
     <t>230155</t>
   </si>
   <si>
@@ -178,9 +184,6 @@
     <t>230212</t>
   </si>
   <si>
-    <t>230121</t>
-  </si>
-  <si>
     <t>230065</t>
   </si>
   <si>
@@ -223,9 +226,6 @@
     <t>230407</t>
   </si>
   <si>
-    <t>230100</t>
-  </si>
-  <si>
     <t>230687</t>
   </si>
   <si>
@@ -304,6 +304,9 @@
     <t>230017</t>
   </si>
   <si>
+    <t>230164</t>
+  </si>
+  <si>
     <t>230052</t>
   </si>
   <si>
@@ -346,9 +349,6 @@
     <t>230033</t>
   </si>
   <si>
-    <t>230164</t>
-  </si>
-  <si>
     <t>230477</t>
   </si>
   <si>
@@ -469,10 +469,10 @@
     <t>12(80.0%)</t>
   </si>
   <si>
-    <t>23(23.0%)</t>
-  </si>
-  <si>
-    <t>56(48.7%)</t>
+    <t>24(24.0%)</t>
+  </si>
+  <si>
+    <t>57(49.6%)</t>
   </si>
   <si>
     <t>44(38.3%)</t>
@@ -505,7 +505,7 @@
     <t>3(20.0%)</t>
   </si>
   <si>
-    <t>34(34.0%)</t>
+    <t>33(33.0%)</t>
   </si>
   <si>
     <t>21(18.3%)</t>
@@ -529,7 +529,7 @@
     <t>15(15.0%)</t>
   </si>
   <si>
-    <t>19(16.5%)</t>
+    <t>18(15.7%)</t>
   </si>
   <si>
     <t>4(3.5%)</t>
@@ -1232,7 +1232,7 @@
         <v>4</v>
       </c>
       <c r="R4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S4" t="s">
         <v>163</v>
@@ -1318,7 +1318,7 @@
         <v>4</v>
       </c>
       <c r="R5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S5" t="s">
         <v>170</v>
@@ -1490,7 +1490,7 @@
         <v>4</v>
       </c>
       <c r="R7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S7" t="s">
         <v>185</v>
@@ -2607,7 +2607,7 @@
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -2666,10 +2666,10 @@
         <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K25" t="s">
         <v>19</v>
@@ -2689,7 +2689,7 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
         <v>42</v>
@@ -2701,10 +2701,10 @@
         <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G26" t="s">
         <v>16</v>
@@ -2716,13 +2716,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K26" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="L26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M26" t="s">
         <v>17</v>
@@ -2731,15 +2731,15 @@
         <v>17</v>
       </c>
       <c r="O26">
-        <v>3.964</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
         <v>19</v>
@@ -2763,13 +2763,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K27" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="L27" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="M27" t="s">
         <v>17</v>
@@ -2783,13 +2783,13 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s">
         <v>19</v>
@@ -2798,7 +2798,7 @@
         <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G28" t="s">
         <v>16</v>
@@ -2810,22 +2810,22 @@
         <v>17</v>
       </c>
       <c r="J28" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K28" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L28" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="M28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O28">
-        <v>3.959</v>
+        <v>3.964</v>
       </c>
     </row>
     <row r="29" spans="1:15">
@@ -2836,7 +2836,7 @@
         <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
         <v>19</v>
@@ -2845,19 +2845,19 @@
         <v>16</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" t="s">
         <v>16</v>
       </c>
       <c r="H29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J29" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K29" t="s">
         <v>16</v>
@@ -2866,30 +2866,30 @@
         <v>17</v>
       </c>
       <c r="M29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O29">
-        <v>3.949</v>
+        <v>3.959</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
         <v>16</v>
@@ -2901,13 +2901,13 @@
         <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J30" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K30" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="L30" t="s">
         <v>17</v>
@@ -2919,18 +2919,18 @@
         <v>17</v>
       </c>
       <c r="O30">
-        <v>3.945</v>
+        <v>3.959</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
         <v>48</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
         <v>19</v>
@@ -2945,16 +2945,16 @@
         <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L31" t="s">
         <v>17</v>
@@ -2966,21 +2966,21 @@
         <v>17</v>
       </c>
       <c r="O31">
-        <v>3.945</v>
+        <v>3.949</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
         <v>49</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
         <v>16</v>
@@ -2995,10 +2995,10 @@
         <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K32" t="s">
         <v>19</v>
@@ -3018,13 +3018,13 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
         <v>19</v>
@@ -3045,10 +3045,10 @@
         <v>17</v>
       </c>
       <c r="J33" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K33" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L33" t="s">
         <v>17</v>
@@ -3065,13 +3065,13 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
         <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
@@ -3089,10 +3089,10 @@
         <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K34" t="s">
         <v>19</v>
@@ -3112,13 +3112,13 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
         <v>52</v>
       </c>
       <c r="C35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D35" t="s">
         <v>19</v>
@@ -3142,7 +3142,7 @@
         <v>19</v>
       </c>
       <c r="K35" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L35" t="s">
         <v>17</v>
@@ -3159,13 +3159,13 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D36" t="s">
         <v>19</v>
@@ -3174,7 +3174,7 @@
         <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
         <v>16</v>
@@ -3189,7 +3189,7 @@
         <v>17</v>
       </c>
       <c r="K36" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L36" t="s">
         <v>17</v>
@@ -3206,22 +3206,22 @@
     </row>
     <row r="37" spans="1:15">
       <c r="A37">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E37" t="s">
         <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
         <v>16</v>
@@ -3230,10 +3230,10 @@
         <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J37" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K37" t="s">
         <v>19</v>
@@ -3253,22 +3253,22 @@
     </row>
     <row r="38" spans="1:15">
       <c r="A38">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
         <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s">
         <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G38" t="s">
         <v>16</v>
@@ -3277,13 +3277,13 @@
         <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K38" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L38" t="s">
         <v>17</v>
@@ -3300,13 +3300,13 @@
     </row>
     <row r="39" spans="1:15">
       <c r="A39">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
         <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
         <v>19</v>
@@ -3347,13 +3347,13 @@
     </row>
     <row r="40" spans="1:15">
       <c r="A40">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
         <v>57</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
         <v>19</v>
@@ -3394,13 +3394,13 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
         <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
         <v>19</v>
@@ -3441,13 +3441,13 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
         <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D42" t="s">
         <v>19</v>
@@ -3456,7 +3456,7 @@
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G42" t="s">
         <v>16</v>
@@ -3468,7 +3468,7 @@
         <v>17</v>
       </c>
       <c r="J42" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K42" t="s">
         <v>19</v>
@@ -3488,13 +3488,13 @@
     </row>
     <row r="43" spans="1:15">
       <c r="A43">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
         <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
         <v>19</v>
@@ -3515,10 +3515,10 @@
         <v>17</v>
       </c>
       <c r="J43" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K43" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L43" t="s">
         <v>17</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="44" spans="1:15">
       <c r="A44">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
         <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G44" t="s">
         <v>16</v>
@@ -3565,16 +3565,16 @@
         <v>19</v>
       </c>
       <c r="K44" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L44" t="s">
         <v>17</v>
       </c>
       <c r="M44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O44">
         <v>3.945</v>
@@ -3582,28 +3582,28 @@
     </row>
     <row r="45" spans="1:15">
       <c r="A45">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
         <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E45" t="s">
         <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G45" t="s">
         <v>16</v>
       </c>
       <c r="H45" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
         <v>17</v>
@@ -3612,30 +3612,30 @@
         <v>19</v>
       </c>
       <c r="K45" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L45" t="s">
         <v>17</v>
       </c>
       <c r="M45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O45">
-        <v>3.925</v>
+        <v>3.945</v>
       </c>
     </row>
     <row r="46" spans="1:15">
       <c r="A46">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
         <v>63</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
         <v>19</v>
@@ -3647,19 +3647,19 @@
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I46" t="s">
         <v>17</v>
       </c>
       <c r="J46" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K46" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L46" t="s">
         <v>17</v>
@@ -3676,34 +3676,34 @@
     </row>
     <row r="47" spans="1:15">
       <c r="A47">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
         <v>64</v>
       </c>
       <c r="C47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D47" t="s">
         <v>19</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I47" t="s">
         <v>17</v>
       </c>
       <c r="J47" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K47" t="s">
         <v>19</v>
@@ -3723,28 +3723,28 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
         <v>65</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="H48" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I48" t="s">
         <v>17</v>
@@ -3759,13 +3759,13 @@
         <v>17</v>
       </c>
       <c r="M48" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O48">
-        <v>3.918</v>
+        <v>3.925</v>
       </c>
     </row>
     <row r="49" spans="1:15">
@@ -3779,7 +3779,7 @@
         <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E49" t="s">
         <v>16</v>
@@ -3788,19 +3788,19 @@
         <v>17</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K49" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="L49" t="s">
         <v>17</v>
@@ -3812,51 +3812,51 @@
         <v>16</v>
       </c>
       <c r="O49">
-        <v>3.904</v>
+        <v>3.918</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" t="s">
+        <v>19</v>
+      </c>
+      <c r="J50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" t="s">
         <v>68</v>
       </c>
-      <c r="C50" t="s">
-        <v>43</v>
-      </c>
-      <c r="D50" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" t="s">
-        <v>19</v>
-      </c>
-      <c r="F50" t="s">
-        <v>16</v>
-      </c>
-      <c r="G50" t="s">
-        <v>16</v>
-      </c>
-      <c r="H50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I50" t="s">
-        <v>19</v>
-      </c>
-      <c r="J50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K50" t="s">
-        <v>43</v>
-      </c>
       <c r="L50" t="s">
         <v>17</v>
       </c>
       <c r="M50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O50">
         <v>3.904</v>
@@ -3864,13 +3864,13 @@
     </row>
     <row r="51" spans="1:15">
       <c r="A51">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
         <v>69</v>
       </c>
       <c r="C51" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D51" t="s">
         <v>19</v>
@@ -3888,13 +3888,13 @@
         <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J51" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K51" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L51" t="s">
         <v>17</v>
@@ -3917,7 +3917,7 @@
         <v>70</v>
       </c>
       <c r="C52" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
         <v>19</v>
@@ -3932,7 +3932,7 @@
         <v>16</v>
       </c>
       <c r="H52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I52" t="s">
         <v>17</v>
@@ -3964,10 +3964,10 @@
         <v>71</v>
       </c>
       <c r="C53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E53" t="s">
         <v>16</v>
@@ -4011,10 +4011,10 @@
         <v>72</v>
       </c>
       <c r="C54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E54" t="s">
         <v>16</v>
@@ -4058,7 +4058,7 @@
         <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D55" t="s">
         <v>19</v>
@@ -4105,7 +4105,7 @@
         <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D56" t="s">
         <v>19</v>
@@ -4152,7 +4152,7 @@
         <v>75</v>
       </c>
       <c r="C57" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D57" t="s">
         <v>16</v>
@@ -4170,13 +4170,13 @@
         <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J57" t="s">
         <v>17</v>
       </c>
       <c r="K57" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L57" t="s">
         <v>17</v>
@@ -4217,13 +4217,13 @@
         <v>17</v>
       </c>
       <c r="I58" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J58" t="s">
         <v>17</v>
       </c>
       <c r="K58" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L58" t="s">
         <v>17</v>
@@ -4246,7 +4246,7 @@
         <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D59" t="s">
         <v>19</v>
@@ -4267,7 +4267,7 @@
         <v>17</v>
       </c>
       <c r="J59" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K59" t="s">
         <v>16</v>
@@ -4293,13 +4293,13 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D60" t="s">
         <v>19</v>
       </c>
       <c r="E60" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F60" t="s">
         <v>16</v>
@@ -4343,7 +4343,7 @@
         <v>19</v>
       </c>
       <c r="D61" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E61" t="s">
         <v>16</v>
@@ -4364,7 +4364,7 @@
         <v>19</v>
       </c>
       <c r="K61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L61" t="s">
         <v>17</v>
@@ -4387,10 +4387,10 @@
         <v>80</v>
       </c>
       <c r="C62" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D62" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
@@ -4411,7 +4411,7 @@
         <v>16</v>
       </c>
       <c r="K62" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L62" t="s">
         <v>17</v>
@@ -4434,7 +4434,7 @@
         <v>81</v>
       </c>
       <c r="C63" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D63" t="s">
         <v>19</v>
@@ -4449,7 +4449,7 @@
         <v>16</v>
       </c>
       <c r="H63" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I63" t="s">
         <v>19</v>
@@ -4458,7 +4458,7 @@
         <v>17</v>
       </c>
       <c r="K63" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L63" t="s">
         <v>17</v>
@@ -4481,7 +4481,7 @@
         <v>82</v>
       </c>
       <c r="C64" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -4496,7 +4496,7 @@
         <v>16</v>
       </c>
       <c r="H64" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I64" t="s">
         <v>17</v>
@@ -4505,7 +4505,7 @@
         <v>19</v>
       </c>
       <c r="K64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L64" t="s">
         <v>17</v>
@@ -4578,7 +4578,7 @@
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E66" t="s">
         <v>16</v>
@@ -4593,19 +4593,19 @@
         <v>17</v>
       </c>
       <c r="I66" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J66" t="s">
         <v>17</v>
       </c>
       <c r="K66" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L66" t="s">
         <v>17</v>
       </c>
       <c r="M66" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N66" t="s">
         <v>16</v>
@@ -4646,7 +4646,7 @@
         <v>17</v>
       </c>
       <c r="K67" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L67" t="s">
         <v>17</v>
@@ -4716,10 +4716,10 @@
         <v>88</v>
       </c>
       <c r="C69" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D69" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
@@ -4813,7 +4813,7 @@
         <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E71" t="s">
         <v>19</v>
@@ -4857,10 +4857,10 @@
         <v>91</v>
       </c>
       <c r="C72" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E72" t="s">
         <v>16</v>
@@ -4875,13 +4875,13 @@
         <v>17</v>
       </c>
       <c r="I72" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J72" t="s">
         <v>17</v>
       </c>
       <c r="K72" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L72" t="s">
         <v>17</v>
@@ -4907,7 +4907,7 @@
         <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E73" t="s">
         <v>84</v>
@@ -4919,7 +4919,7 @@
         <v>16</v>
       </c>
       <c r="H73" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I73" t="s">
         <v>19</v>
@@ -4954,7 +4954,7 @@
         <v>19</v>
       </c>
       <c r="D74" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E74" t="s">
         <v>19</v>
@@ -4966,16 +4966,16 @@
         <v>16</v>
       </c>
       <c r="H74" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I74" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J74" t="s">
         <v>17</v>
       </c>
       <c r="K74" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L74" t="s">
         <v>17</v>
@@ -5001,7 +5001,7 @@
         <v>19</v>
       </c>
       <c r="D75" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
@@ -5019,13 +5019,13 @@
         <v>17</v>
       </c>
       <c r="J75" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K75" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L75" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M75" t="s">
         <v>17</v>
@@ -5048,7 +5048,7 @@
         <v>19</v>
       </c>
       <c r="D76" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E76" t="s">
         <v>16</v>
@@ -5066,10 +5066,10 @@
         <v>17</v>
       </c>
       <c r="J76" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K76" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L76" t="s">
         <v>17</v>
@@ -5092,43 +5092,43 @@
         <v>96</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D77" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E77" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G77" t="s">
         <v>16</v>
       </c>
       <c r="H77" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="I77" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="J77" t="s">
         <v>17</v>
       </c>
       <c r="K77" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="L77" t="s">
         <v>17</v>
       </c>
       <c r="M77" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N77" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O77">
-        <v>3.768</v>
+        <v>3.775</v>
       </c>
     </row>
     <row r="78" spans="1:15">
@@ -5139,16 +5139,16 @@
         <v>97</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="F78" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G78" t="s">
         <v>16</v>
@@ -5157,60 +5157,60 @@
         <v>17</v>
       </c>
       <c r="I78" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="J78" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K78" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="L78" t="s">
         <v>17</v>
       </c>
       <c r="M78" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O78">
-        <v>3.763</v>
+        <v>3.768</v>
       </c>
     </row>
     <row r="79" spans="1:15">
       <c r="A79">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B79" t="s">
         <v>98</v>
       </c>
       <c r="C79" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G79" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J79" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K79" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L79" t="s">
         <v>17</v>
@@ -5227,37 +5227,37 @@
     </row>
     <row r="80" spans="1:15">
       <c r="A80">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" t="s">
         <v>100</v>
       </c>
-      <c r="C80" t="s">
-        <v>67</v>
-      </c>
       <c r="D80" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E80" t="s">
         <v>19</v>
       </c>
       <c r="F80" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G80" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H80" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J80" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="K80" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="L80" t="s">
         <v>17</v>
@@ -5269,7 +5269,7 @@
         <v>17</v>
       </c>
       <c r="O80">
-        <v>3.758</v>
+        <v>3.763</v>
       </c>
     </row>
     <row r="81" spans="1:15">
@@ -5280,13 +5280,13 @@
         <v>101</v>
       </c>
       <c r="C81" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="D81" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E81" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F81" t="s">
         <v>19</v>
@@ -5295,16 +5295,16 @@
         <v>16</v>
       </c>
       <c r="H81" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J81" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K81" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="L81" t="s">
         <v>17</v>
@@ -5316,7 +5316,7 @@
         <v>17</v>
       </c>
       <c r="O81">
-        <v>3.75</v>
+        <v>3.758</v>
       </c>
     </row>
     <row r="82" spans="1:15">
@@ -5327,25 +5327,25 @@
         <v>102</v>
       </c>
       <c r="C82" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="D82" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E82" t="s">
         <v>16</v>
       </c>
       <c r="F82" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G82" t="s">
         <v>16</v>
       </c>
       <c r="H82" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="I82" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J82" t="s">
         <v>17</v>
@@ -5363,42 +5363,42 @@
         <v>17</v>
       </c>
       <c r="O82">
-        <v>3.745</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="83" spans="1:15">
       <c r="A83">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B83" t="s">
         <v>103</v>
       </c>
       <c r="C83" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D83" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="E83" t="s">
         <v>16</v>
       </c>
       <c r="F83" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G83" t="s">
         <v>16</v>
       </c>
       <c r="H83" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I83" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="J83" t="s">
         <v>17</v>
       </c>
       <c r="K83" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L83" t="s">
         <v>17</v>
@@ -5415,37 +5415,37 @@
     </row>
     <row r="84" spans="1:15">
       <c r="A84">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" t="s">
         <v>104</v>
       </c>
       <c r="C84" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D84" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E84" t="s">
         <v>16</v>
       </c>
       <c r="F84" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G84" t="s">
         <v>16</v>
       </c>
       <c r="H84" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="I84" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="J84" t="s">
         <v>17</v>
       </c>
       <c r="K84" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L84" t="s">
         <v>17</v>
@@ -5457,7 +5457,7 @@
         <v>17</v>
       </c>
       <c r="O84">
-        <v>3.741</v>
+        <v>3.745</v>
       </c>
     </row>
     <row r="85" spans="1:15">
@@ -5468,13 +5468,13 @@
         <v>105</v>
       </c>
       <c r="C85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D85" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="E85" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F85" t="s">
         <v>16</v>
@@ -5483,16 +5483,16 @@
         <v>16</v>
       </c>
       <c r="H85" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I85" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="J85" t="s">
         <v>17</v>
       </c>
       <c r="K85" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="L85" t="s">
         <v>17</v>
@@ -5504,7 +5504,7 @@
         <v>17</v>
       </c>
       <c r="O85">
-        <v>3.736</v>
+        <v>3.741</v>
       </c>
     </row>
     <row r="86" spans="1:15">
@@ -5515,16 +5515,16 @@
         <v>106</v>
       </c>
       <c r="C86" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="D86" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G86" t="s">
         <v>16</v>
@@ -5533,13 +5533,13 @@
         <v>17</v>
       </c>
       <c r="I86" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J86" t="s">
         <v>17</v>
       </c>
       <c r="K86" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="L86" t="s">
         <v>17</v>
@@ -5551,22 +5551,22 @@
         <v>17</v>
       </c>
       <c r="O86">
-        <v>3.722</v>
+        <v>3.736</v>
       </c>
     </row>
     <row r="87" spans="1:15">
       <c r="A87">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B87" t="s">
         <v>107</v>
       </c>
       <c r="C87" t="s">
+        <v>44</v>
+      </c>
+      <c r="D87" t="s">
         <v>84</v>
       </c>
-      <c r="D87" t="s">
-        <v>43</v>
-      </c>
       <c r="E87" t="s">
         <v>19</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>17</v>
       </c>
       <c r="I87" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J87" t="s">
         <v>17</v>
@@ -5603,34 +5603,34 @@
     </row>
     <row r="88" spans="1:15">
       <c r="A88">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B88" t="s">
         <v>108</v>
       </c>
       <c r="C88" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D88" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="E88" t="s">
         <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G88" t="s">
         <v>16</v>
       </c>
       <c r="H88" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="J88" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K88" t="s">
         <v>19</v>
@@ -5645,18 +5645,18 @@
         <v>17</v>
       </c>
       <c r="O88">
-        <v>3.716</v>
+        <v>3.722</v>
       </c>
     </row>
     <row r="89" spans="1:15">
       <c r="A89">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B89" t="s">
         <v>109</v>
       </c>
       <c r="C89" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D89" t="s">
         <v>84</v>
@@ -5671,13 +5671,13 @@
         <v>16</v>
       </c>
       <c r="H89" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K89" t="s">
         <v>19</v>
@@ -5697,16 +5697,16 @@
     </row>
     <row r="90" spans="1:15">
       <c r="A90">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B90" t="s">
         <v>110</v>
       </c>
       <c r="C90" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D90" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
@@ -5718,7 +5718,7 @@
         <v>16</v>
       </c>
       <c r="H90" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="I90" t="s">
         <v>19</v>
@@ -5727,7 +5727,7 @@
         <v>17</v>
       </c>
       <c r="K90" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L90" t="s">
         <v>17</v>
@@ -5739,7 +5739,7 @@
         <v>17</v>
       </c>
       <c r="O90">
-        <v>3.708</v>
+        <v>3.716</v>
       </c>
     </row>
     <row r="91" spans="1:15">
@@ -5750,10 +5750,10 @@
         <v>111</v>
       </c>
       <c r="C91" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D91" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E91" t="s">
         <v>19</v>
@@ -5765,7 +5765,7 @@
         <v>16</v>
       </c>
       <c r="H91" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I91" t="s">
         <v>17</v>
@@ -5774,7 +5774,7 @@
         <v>19</v>
       </c>
       <c r="K91" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L91" t="s">
         <v>17</v>
@@ -5800,7 +5800,7 @@
         <v>17</v>
       </c>
       <c r="D92" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E92" t="s">
         <v>19</v>
@@ -5815,7 +5815,7 @@
         <v>17</v>
       </c>
       <c r="I92" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J92" t="s">
         <v>17</v>
@@ -5844,10 +5844,10 @@
         <v>113</v>
       </c>
       <c r="C93" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E93" t="s">
         <v>19</v>
@@ -5894,7 +5894,7 @@
         <v>84</v>
       </c>
       <c r="D94" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E94" t="s">
         <v>16</v>
@@ -5909,7 +5909,7 @@
         <v>19</v>
       </c>
       <c r="I94" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J94" t="s">
         <v>17</v>
@@ -5941,7 +5941,7 @@
         <v>84</v>
       </c>
       <c r="D95" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E95" t="s">
         <v>19</v>
@@ -5962,7 +5962,7 @@
         <v>19</v>
       </c>
       <c r="K95" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L95" t="s">
         <v>17</v>
@@ -5988,7 +5988,7 @@
         <v>84</v>
       </c>
       <c r="D96" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E96" t="s">
         <v>19</v>
@@ -6009,7 +6009,7 @@
         <v>17</v>
       </c>
       <c r="K96" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L96" t="s">
         <v>17</v>
@@ -6035,7 +6035,7 @@
         <v>84</v>
       </c>
       <c r="D97" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E97" t="s">
         <v>19</v>
@@ -6044,7 +6044,7 @@
         <v>19</v>
       </c>
       <c r="G97" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -6053,10 +6053,10 @@
         <v>17</v>
       </c>
       <c r="J97" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K97" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L97" t="s">
         <v>17</v>
@@ -6082,7 +6082,7 @@
         <v>84</v>
       </c>
       <c r="D98" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E98" t="s">
         <v>16</v>
@@ -6097,7 +6097,7 @@
         <v>17</v>
       </c>
       <c r="I98" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J98" t="s">
         <v>17</v>
@@ -6126,10 +6126,10 @@
         <v>119</v>
       </c>
       <c r="C99" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E99" t="s">
         <v>16</v>
@@ -6144,7 +6144,7 @@
         <v>17</v>
       </c>
       <c r="I99" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J99" t="s">
         <v>17</v>
@@ -6173,13 +6173,13 @@
         <v>120</v>
       </c>
       <c r="C100" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E100" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F100" t="s">
         <v>19</v>
@@ -6191,13 +6191,13 @@
         <v>17</v>
       </c>
       <c r="I100" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J100" t="s">
         <v>17</v>
       </c>
       <c r="K100" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L100" t="s">
         <v>17</v>
@@ -6220,10 +6220,10 @@
         <v>121</v>
       </c>
       <c r="C101" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D101" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E101" t="s">
         <v>16</v>
@@ -6267,10 +6267,10 @@
         <v>122</v>
       </c>
       <c r="C102" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D102" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E102" t="s">
         <v>19</v>
@@ -6288,7 +6288,7 @@
         <v>17</v>
       </c>
       <c r="J102" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K102" t="s">
         <v>19</v>
@@ -6314,7 +6314,7 @@
         <v>123</v>
       </c>
       <c r="C103" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D103" t="s">
         <v>19</v>
@@ -6332,13 +6332,13 @@
         <v>17</v>
       </c>
       <c r="I103" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J103" t="s">
         <v>17</v>
       </c>
       <c r="K103" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L103" t="s">
         <v>17</v>
@@ -6361,16 +6361,16 @@
         <v>124</v>
       </c>
       <c r="C104" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D104" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E104" t="s">
         <v>16</v>
       </c>
       <c r="F104" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G104" t="s">
         <v>19</v>
@@ -6382,10 +6382,10 @@
         <v>17</v>
       </c>
       <c r="J104" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K104" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L104" t="s">
         <v>17</v>
@@ -6414,7 +6414,7 @@
         <v>84</v>
       </c>
       <c r="E105" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F105" t="s">
         <v>17</v>
@@ -6426,19 +6426,19 @@
         <v>17</v>
       </c>
       <c r="I105" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J105" t="s">
         <v>17</v>
       </c>
       <c r="K105" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L105" t="s">
         <v>17</v>
       </c>
       <c r="M105" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N105" t="s">
         <v>19</v>
@@ -6458,22 +6458,22 @@
         <v>17</v>
       </c>
       <c r="D106" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E106" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F106" t="s">
         <v>17</v>
       </c>
       <c r="G106" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
       </c>
       <c r="I106" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J106" t="s">
         <v>17</v>
@@ -6485,7 +6485,7 @@
         <v>17</v>
       </c>
       <c r="M106" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N106" t="s">
         <v>16</v>
@@ -6502,13 +6502,13 @@
         <v>127</v>
       </c>
       <c r="C107" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D107" t="s">
         <v>84</v>
       </c>
       <c r="E107" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F107" t="s">
         <v>19</v>
@@ -6552,10 +6552,10 @@
         <v>84</v>
       </c>
       <c r="D108" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E108" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F108" t="s">
         <v>19</v>
@@ -6567,7 +6567,7 @@
         <v>17</v>
       </c>
       <c r="I108" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J108" t="s">
         <v>17</v>
@@ -6599,10 +6599,10 @@
         <v>130</v>
       </c>
       <c r="D109" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E109" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F109" t="s">
         <v>19</v>
@@ -6614,7 +6614,7 @@
         <v>17</v>
       </c>
       <c r="I109" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J109" t="s">
         <v>17</v>
@@ -6643,7 +6643,7 @@
         <v>131</v>
       </c>
       <c r="C110" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D110" t="s">
         <v>84</v>
@@ -6661,7 +6661,7 @@
         <v>17</v>
       </c>
       <c r="I110" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J110" t="s">
         <v>17</v>
@@ -6711,10 +6711,10 @@
         <v>17</v>
       </c>
       <c r="J111" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K111" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L111" t="s">
         <v>17</v>
@@ -6752,7 +6752,7 @@
         <v>19</v>
       </c>
       <c r="H112" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I112" t="s">
         <v>19</v>
@@ -6761,7 +6761,7 @@
         <v>17</v>
       </c>
       <c r="K112" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L112" t="s">
         <v>17</v>
@@ -6784,13 +6784,13 @@
         <v>135</v>
       </c>
       <c r="C113" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D113" t="s">
         <v>133</v>
       </c>
       <c r="E113" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F113" t="s">
         <v>19</v>
@@ -6799,16 +6799,16 @@
         <v>19</v>
       </c>
       <c r="H113" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I113" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J113" t="s">
         <v>17</v>
       </c>
       <c r="K113" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L113" t="s">
         <v>17</v>
@@ -6834,13 +6834,13 @@
         <v>133</v>
       </c>
       <c r="D114" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E114" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F114" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G114" t="s">
         <v>19</v>
@@ -6881,28 +6881,28 @@
         <v>130</v>
       </c>
       <c r="D115" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E115" t="s">
         <v>84</v>
       </c>
       <c r="F115" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G115" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H115" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I115" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J115" t="s">
         <v>17</v>
       </c>
       <c r="K115" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L115" t="s">
         <v>17</v>
@@ -6934,7 +6934,7 @@
         <v>19</v>
       </c>
       <c r="F116" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G116" t="s">
         <v>133</v>
@@ -6943,7 +6943,7 @@
         <v>17</v>
       </c>
       <c r="I116" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J116" t="s">
         <v>17</v>

--- a/output/Results - sem4.xlsx
+++ b/output/Results - sem4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="201">
   <si>
     <t>Rank</t>
   </si>
@@ -58,6 +58,9 @@
     <t>BM2012</t>
   </si>
   <si>
+    <t>MA2054</t>
+  </si>
+  <si>
     <t>SGPA</t>
   </si>
   <si>
@@ -91,24 +94,24 @@
     <t>230258</t>
   </si>
   <si>
+    <t>230481</t>
+  </si>
+  <si>
     <t>230051</t>
   </si>
   <si>
-    <t>230481</t>
+    <t>230138</t>
+  </si>
+  <si>
+    <t>230680</t>
+  </si>
+  <si>
+    <t>230186</t>
   </si>
   <si>
     <t>230566</t>
   </si>
   <si>
-    <t>230138</t>
-  </si>
-  <si>
-    <t>230680</t>
-  </si>
-  <si>
-    <t>230186</t>
-  </si>
-  <si>
     <t>230322</t>
   </si>
   <si>
@@ -118,213 +121,219 @@
     <t>230218</t>
   </si>
   <si>
+    <t>230332</t>
+  </si>
+  <si>
+    <t>230544</t>
+  </si>
+  <si>
+    <t>230197</t>
+  </si>
+  <si>
+    <t>230121</t>
+  </si>
+  <si>
+    <t>230355</t>
+  </si>
+  <si>
+    <t>230470</t>
+  </si>
+  <si>
+    <t>230486</t>
+  </si>
+  <si>
     <t>230353</t>
   </si>
   <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>230539</t>
+  </si>
+  <si>
+    <t>230521</t>
+  </si>
+  <si>
+    <t>230108</t>
+  </si>
+  <si>
+    <t>230100</t>
+  </si>
+  <si>
+    <t>230155</t>
+  </si>
+  <si>
+    <t>230074</t>
+  </si>
+  <si>
+    <t>230318</t>
+  </si>
+  <si>
+    <t>230256</t>
+  </si>
+  <si>
+    <t>230261</t>
+  </si>
+  <si>
+    <t>230212</t>
+  </si>
+  <si>
+    <t>230375</t>
+  </si>
+  <si>
+    <t>230659</t>
+  </si>
+  <si>
+    <t>230395</t>
+  </si>
+  <si>
+    <t>230487</t>
+  </si>
+  <si>
+    <t>230507</t>
+  </si>
+  <si>
     <t>230735</t>
   </si>
   <si>
-    <t>230332</t>
-  </si>
-  <si>
-    <t>230197</t>
-  </si>
-  <si>
-    <t>230544</t>
-  </si>
-  <si>
-    <t>230121</t>
-  </si>
-  <si>
-    <t>230355</t>
-  </si>
-  <si>
-    <t>230470</t>
-  </si>
-  <si>
-    <t>230486</t>
-  </si>
-  <si>
-    <t>230539</t>
-  </si>
-  <si>
-    <t>A-</t>
-  </si>
-  <si>
-    <t>230521</t>
-  </si>
-  <si>
-    <t>230108</t>
-  </si>
-  <si>
-    <t>230100</t>
-  </si>
-  <si>
-    <t>230155</t>
+    <t>B+</t>
   </si>
   <si>
     <t>230045</t>
   </si>
   <si>
-    <t>230074</t>
+    <t>230038</t>
+  </si>
+  <si>
+    <t>230195</t>
+  </si>
+  <si>
+    <t>230492</t>
+  </si>
+  <si>
+    <t>230727</t>
+  </si>
+  <si>
+    <t>230159</t>
+  </si>
+  <si>
+    <t>230407</t>
+  </si>
+  <si>
+    <t>230147</t>
+  </si>
+  <si>
+    <t>230687</t>
+  </si>
+  <si>
+    <t>230300</t>
+  </si>
+  <si>
+    <t>230724</t>
+  </si>
+  <si>
+    <t>230082</t>
+  </si>
+  <si>
+    <t>230508</t>
+  </si>
+  <si>
+    <t>230563</t>
+  </si>
+  <si>
+    <t>230065</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>230390</t>
+  </si>
+  <si>
+    <t>230180</t>
+  </si>
+  <si>
+    <t>230473</t>
   </si>
   <si>
     <t>230502</t>
   </si>
   <si>
-    <t>230318</t>
-  </si>
-  <si>
-    <t>230256</t>
-  </si>
-  <si>
-    <t>230261</t>
-  </si>
-  <si>
-    <t>230212</t>
-  </si>
-  <si>
-    <t>230065</t>
-  </si>
-  <si>
-    <t>230147</t>
-  </si>
-  <si>
-    <t>230375</t>
-  </si>
-  <si>
-    <t>230659</t>
-  </si>
-  <si>
-    <t>230395</t>
-  </si>
-  <si>
-    <t>230487</t>
-  </si>
-  <si>
-    <t>230507</t>
-  </si>
-  <si>
-    <t>230038</t>
-  </si>
-  <si>
-    <t>230195</t>
-  </si>
-  <si>
-    <t>230492</t>
-  </si>
-  <si>
-    <t>230727</t>
-  </si>
-  <si>
-    <t>230159</t>
-  </si>
-  <si>
-    <t>B+</t>
-  </si>
-  <si>
-    <t>230407</t>
-  </si>
-  <si>
-    <t>230687</t>
-  </si>
-  <si>
-    <t>230300</t>
-  </si>
-  <si>
-    <t>230724</t>
-  </si>
-  <si>
-    <t>230508</t>
-  </si>
-  <si>
-    <t>230563</t>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>230564</t>
+  </si>
+  <si>
+    <t>230469</t>
+  </si>
+  <si>
+    <t>230077</t>
+  </si>
+  <si>
+    <t>230444</t>
+  </si>
+  <si>
+    <t>230417</t>
+  </si>
+  <si>
+    <t>230726</t>
+  </si>
+  <si>
+    <t>230070</t>
   </si>
   <si>
     <t>230130</t>
   </si>
   <si>
-    <t>230390</t>
-  </si>
-  <si>
-    <t>230180</t>
-  </si>
-  <si>
-    <t>230082</t>
-  </si>
-  <si>
-    <t>230473</t>
+    <t>230581</t>
+  </si>
+  <si>
+    <t>230500</t>
+  </si>
+  <si>
+    <t>230629</t>
+  </si>
+  <si>
+    <t>230654</t>
+  </si>
+  <si>
+    <t>230145</t>
+  </si>
+  <si>
+    <t>230017</t>
   </si>
   <si>
     <t>230527</t>
   </si>
   <si>
-    <t>230564</t>
-  </si>
-  <si>
-    <t>230469</t>
+    <t>230493</t>
+  </si>
+  <si>
+    <t>230164</t>
+  </si>
+  <si>
+    <t>230477</t>
+  </si>
+  <si>
+    <t>230052</t>
+  </si>
+  <si>
+    <t>230058</t>
+  </si>
+  <si>
+    <t>230525</t>
+  </si>
+  <si>
+    <t>230495</t>
+  </si>
+  <si>
+    <t>230526</t>
   </si>
   <si>
     <t>230536</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>230077</t>
-  </si>
-  <si>
-    <t>230444</t>
-  </si>
-  <si>
-    <t>230417</t>
-  </si>
-  <si>
-    <t>230726</t>
-  </si>
-  <si>
-    <t>230070</t>
-  </si>
-  <si>
-    <t>230581</t>
-  </si>
-  <si>
-    <t>230500</t>
-  </si>
-  <si>
-    <t>230629</t>
-  </si>
-  <si>
-    <t>230654</t>
-  </si>
-  <si>
-    <t>230145</t>
-  </si>
-  <si>
-    <t>230017</t>
-  </si>
-  <si>
-    <t>230164</t>
-  </si>
-  <si>
-    <t>230052</t>
-  </si>
-  <si>
-    <t>230058</t>
-  </si>
-  <si>
-    <t>230525</t>
-  </si>
-  <si>
-    <t>B-</t>
-  </si>
-  <si>
-    <t>230495</t>
-  </si>
-  <si>
-    <t>230526</t>
-  </si>
-  <si>
     <t>230063</t>
   </si>
   <si>
@@ -337,9 +346,6 @@
     <t>230012</t>
   </si>
   <si>
-    <t>230493</t>
-  </si>
-  <si>
     <t>230650</t>
   </si>
   <si>
@@ -349,21 +355,18 @@
     <t>230033</t>
   </si>
   <si>
-    <t>230477</t>
+    <t>230327</t>
   </si>
   <si>
     <t>230016</t>
   </si>
   <si>
-    <t>230327</t>
+    <t>230585</t>
   </si>
   <si>
     <t>230697</t>
   </si>
   <si>
-    <t>230585</t>
-  </si>
-  <si>
     <t>230280</t>
   </si>
   <si>
@@ -373,15 +376,15 @@
     <t>230468</t>
   </si>
   <si>
+    <t>230229</t>
+  </si>
+  <si>
+    <t>230013</t>
+  </si>
+  <si>
     <t>230140</t>
   </si>
   <si>
-    <t>230229</t>
-  </si>
-  <si>
-    <t>230013</t>
-  </si>
-  <si>
     <t>230175</t>
   </si>
   <si>
@@ -403,15 +406,15 @@
     <t>230613</t>
   </si>
   <si>
+    <t>230224</t>
+  </si>
+  <si>
     <t>230020</t>
   </si>
   <si>
     <t>C+</t>
   </si>
   <si>
-    <t>230224</t>
-  </si>
-  <si>
     <t>230238</t>
   </si>
   <si>
@@ -469,7 +472,10 @@
     <t>12(80.0%)</t>
   </si>
   <si>
-    <t>24(24.0%)</t>
+    <t>3(12.5%)</t>
+  </si>
+  <si>
+    <t>25(25.0%)</t>
   </si>
   <si>
     <t>57(49.6%)</t>
@@ -505,6 +511,9 @@
     <t>3(20.0%)</t>
   </si>
   <si>
+    <t>7(29.2%)</t>
+  </si>
+  <si>
     <t>33(33.0%)</t>
   </si>
   <si>
@@ -526,7 +535,10 @@
     <t>1(12.5%)</t>
   </si>
   <si>
-    <t>15(15.0%)</t>
+    <t>5(20.8%)</t>
+  </si>
+  <si>
+    <t>14(14.0%)</t>
   </si>
   <si>
     <t>18(15.7%)</t>
@@ -556,6 +568,9 @@
     <t>1(6.7%)</t>
   </si>
   <si>
+    <t>4(16.7%)</t>
+  </si>
+  <si>
     <t>12(12.0%)</t>
   </si>
   <si>
@@ -571,6 +586,9 @@
     <t>1(1.8%)</t>
   </si>
   <si>
+    <t>2(8.3%)</t>
+  </si>
+  <si>
     <t>5(5.0%)</t>
   </si>
   <si>
@@ -578,6 +596,9 @@
   </si>
   <si>
     <t>2(2.0%)</t>
+  </si>
+  <si>
+    <t>1(4.2%)</t>
   </si>
   <si>
     <t>C</t>
@@ -927,10 +948,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD116"/>
+  <dimension ref="A1:AF116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:32">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -976,94 +997,100 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="S1" t="s">
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" t="s">
         <v>2</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>3</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>4</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>5</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>6</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>8</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>9</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>10</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>11</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>12</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AF1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2">
+        <v>18</v>
+      </c>
+      <c r="O2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2">
         <v>4</v>
       </c>
-      <c r="R2" t="s">
-        <v>16</v>
-      </c>
       <c r="S2" t="s">
-        <v>139</v>
+        <v>17</v>
       </c>
       <c r="T2" t="s">
         <v>140</v>
@@ -1098,559 +1125,601 @@
       <c r="AD2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="3" spans="1:30">
+      <c r="AE2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3">
+        <v>18</v>
+      </c>
+      <c r="O3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3">
         <v>4</v>
       </c>
-      <c r="R3" t="s">
-        <v>19</v>
-      </c>
       <c r="S3" t="s">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="T3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="U3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="W3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="X3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AB3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AC3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30">
+        <v>163</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>164</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O4">
+        <v>18</v>
+      </c>
+      <c r="O4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4">
         <v>4</v>
       </c>
-      <c r="R4" t="s">
-        <v>44</v>
-      </c>
       <c r="S4" t="s">
-        <v>163</v>
+        <v>43</v>
       </c>
       <c r="T4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="U4" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="V4" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="W4" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="X4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Y4" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB4" t="s">
         <v>167</v>
       </c>
-      <c r="Z4" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>164</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>169</v>
-      </c>
       <c r="AC4" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="AD4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30">
+        <v>150</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N5" t="s">
-        <v>17</v>
-      </c>
-      <c r="O5">
+        <v>18</v>
+      </c>
+      <c r="O5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P5">
         <v>4</v>
       </c>
-      <c r="R5" t="s">
-        <v>68</v>
-      </c>
       <c r="S5" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="T5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="U5" t="s">
+        <v>175</v>
+      </c>
+      <c r="V5" t="s">
+        <v>176</v>
+      </c>
+      <c r="W5" t="s">
+        <v>177</v>
+      </c>
+      <c r="X5" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>179</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>182</v>
+      </c>
+      <c r="AC5" t="s">
         <v>172</v>
       </c>
-      <c r="V5" t="s">
-        <v>173</v>
-      </c>
-      <c r="W5" t="s">
-        <v>174</v>
-      </c>
-      <c r="X5" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>169</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>179</v>
-      </c>
       <c r="AD5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30">
+        <v>183</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O6">
+        <v>18</v>
+      </c>
+      <c r="O6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P6">
         <v>4</v>
       </c>
-      <c r="R6" t="s">
-        <v>84</v>
-      </c>
       <c r="S6" t="s">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="T6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="U6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="V6" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="W6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="X6" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="Y6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Z6" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="AA6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="AB6" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="AC6" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="AD6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30">
+        <v>149</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N7" t="s">
-        <v>17</v>
-      </c>
-      <c r="O7">
+        <v>18</v>
+      </c>
+      <c r="O7" t="s">
+        <v>18</v>
+      </c>
+      <c r="P7">
         <v>4</v>
       </c>
-      <c r="R7" t="s">
-        <v>100</v>
-      </c>
       <c r="S7" t="s">
-        <v>185</v>
+        <v>81</v>
       </c>
       <c r="T7" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="U7" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="V7" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="W7" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="X7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y7" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="Z7" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="AA7" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="AB7" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="AC7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30">
+        <v>149</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N8" t="s">
-        <v>17</v>
-      </c>
-      <c r="O8">
+        <v>18</v>
+      </c>
+      <c r="O8" t="s">
+        <v>20</v>
+      </c>
+      <c r="P8">
         <v>4</v>
       </c>
-      <c r="R8" t="s">
-        <v>130</v>
-      </c>
       <c r="S8" t="s">
-        <v>187</v>
+        <v>132</v>
       </c>
       <c r="T8" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="U8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="X8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30">
+        <v>149</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M9" t="s">
         <v>17</v>
@@ -1658,4984 +1727,5308 @@
       <c r="N9" t="s">
         <v>17</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P9">
         <v>4</v>
       </c>
-      <c r="R9" t="s">
-        <v>188</v>
-      </c>
       <c r="S9" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="T9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="X9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD9" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30">
+        <v>149</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N10" t="s">
-        <v>16</v>
-      </c>
-      <c r="O10">
+        <v>18</v>
+      </c>
+      <c r="O10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P10">
         <v>4</v>
       </c>
-      <c r="R10" t="s">
-        <v>189</v>
-      </c>
       <c r="S10" t="s">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="T10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="X10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30">
+        <v>149</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
       </c>
       <c r="K11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N11" t="s">
-        <v>17</v>
-      </c>
-      <c r="O11">
+        <v>18</v>
+      </c>
+      <c r="O11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P11">
         <v>4</v>
       </c>
-      <c r="R11" t="s">
-        <v>190</v>
-      </c>
       <c r="S11" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="T11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="X11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30">
+        <v>149</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N12" t="s">
-        <v>17</v>
-      </c>
-      <c r="O12">
+        <v>18</v>
+      </c>
+      <c r="O12" t="s">
+        <v>18</v>
+      </c>
+      <c r="P12">
         <v>4</v>
       </c>
-      <c r="R12" t="s">
-        <v>191</v>
-      </c>
       <c r="S12" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="T12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="X12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD12" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30">
+        <v>149</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s">
         <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N13" t="s">
-        <v>17</v>
-      </c>
-      <c r="O13">
+        <v>18</v>
+      </c>
+      <c r="O13" t="s">
+        <v>18</v>
+      </c>
+      <c r="P13">
         <v>4</v>
       </c>
-      <c r="R13" t="s">
-        <v>192</v>
-      </c>
       <c r="S13" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="T13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="X13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30">
+        <v>149</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N14" t="s">
-        <v>17</v>
-      </c>
-      <c r="O14">
+        <v>18</v>
+      </c>
+      <c r="O14" t="s">
+        <v>20</v>
+      </c>
+      <c r="P14">
         <v>4</v>
       </c>
-      <c r="R14" t="s">
-        <v>193</v>
-      </c>
       <c r="S14" t="s">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="T14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="W14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="X14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD14" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30">
+        <v>149</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N15" t="s">
-        <v>17</v>
-      </c>
-      <c r="O15">
+        <v>18</v>
+      </c>
+      <c r="O15" t="s">
+        <v>18</v>
+      </c>
+      <c r="P15">
         <v>4</v>
       </c>
-      <c r="R15" t="s">
-        <v>133</v>
-      </c>
       <c r="S15" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="T15" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="U15" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="V15" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="W15" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="X15" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="Y15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AA15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD15" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30">
+        <v>149</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32">
       <c r="A16">
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N16" t="s">
-        <v>17</v>
-      </c>
-      <c r="O16">
+        <v>18</v>
+      </c>
+      <c r="O16" t="s">
+        <v>18</v>
+      </c>
+      <c r="P16">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:16">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>16</v>
-      </c>
-      <c r="O17">
+        <v>17</v>
+      </c>
+      <c r="O17" t="s">
+        <v>18</v>
+      </c>
+      <c r="P17">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:16">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N18" t="s">
         <v>17</v>
       </c>
-      <c r="O18">
+      <c r="O18" t="s">
+        <v>18</v>
+      </c>
+      <c r="P18">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:16">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N19" t="s">
-        <v>17</v>
-      </c>
-      <c r="O19">
+        <v>18</v>
+      </c>
+      <c r="O19" t="s">
+        <v>18</v>
+      </c>
+      <c r="P19">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:16">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F20" t="s">
         <v>17</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N20" t="s">
-        <v>16</v>
-      </c>
-      <c r="O20">
+        <v>18</v>
+      </c>
+      <c r="O20" t="s">
+        <v>20</v>
+      </c>
+      <c r="P20">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:16">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N21" t="s">
-        <v>17</v>
-      </c>
-      <c r="O21">
+        <v>18</v>
+      </c>
+      <c r="O21" t="s">
+        <v>18</v>
+      </c>
+      <c r="P21">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:16">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N22" t="s">
-        <v>17</v>
-      </c>
-      <c r="O22">
+        <v>18</v>
+      </c>
+      <c r="O22" t="s">
+        <v>18</v>
+      </c>
+      <c r="P22">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:16">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N23" t="s">
-        <v>17</v>
-      </c>
-      <c r="O23">
+        <v>18</v>
+      </c>
+      <c r="O23" t="s">
+        <v>18</v>
+      </c>
+      <c r="P23">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:16">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N24" t="s">
-        <v>17</v>
-      </c>
-      <c r="O24">
+        <v>18</v>
+      </c>
+      <c r="O24" t="s">
+        <v>20</v>
+      </c>
+      <c r="P24">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:16">
       <c r="A25">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N25" t="s">
-        <v>17</v>
-      </c>
-      <c r="O25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O25" t="s">
+        <v>43</v>
+      </c>
+      <c r="P25">
+        <v>3.975</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K26" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="L26" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N26" t="s">
-        <v>17</v>
-      </c>
-      <c r="O26">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O26" t="s">
+        <v>18</v>
+      </c>
+      <c r="P26">
+        <v>3.964</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="L27" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="M27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N27" t="s">
-        <v>17</v>
-      </c>
-      <c r="O27">
+        <v>18</v>
+      </c>
+      <c r="O27" t="s">
+        <v>18</v>
+      </c>
+      <c r="P27">
         <v>3.964</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:16">
       <c r="A28">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J28" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L28" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="M28" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N28" t="s">
         <v>17</v>
       </c>
-      <c r="O28">
-        <v>3.964</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="O28" t="s">
+        <v>18</v>
+      </c>
+      <c r="P28">
+        <v>3.959</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F29" t="s">
         <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J29" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="L29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N29" t="s">
-        <v>16</v>
-      </c>
-      <c r="O29">
+        <v>18</v>
+      </c>
+      <c r="O29" t="s">
+        <v>18</v>
+      </c>
+      <c r="P29">
         <v>3.959</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:16">
       <c r="A30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I30" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K30" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N30" t="s">
-        <v>17</v>
-      </c>
-      <c r="O30">
-        <v>3.959</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O30" t="s">
+        <v>18</v>
+      </c>
+      <c r="P30">
+        <v>3.949</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J31" t="s">
         <v>17</v>
       </c>
       <c r="K31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N31" t="s">
-        <v>17</v>
-      </c>
-      <c r="O31">
-        <v>3.949</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O31" t="s">
+        <v>18</v>
+      </c>
+      <c r="P31">
+        <v>3.945</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M32" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N32" t="s">
-        <v>17</v>
-      </c>
-      <c r="O32">
+        <v>18</v>
+      </c>
+      <c r="O32" t="s">
+        <v>18</v>
+      </c>
+      <c r="P32">
         <v>3.945</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:16">
       <c r="A33">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J33" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M33" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>17</v>
-      </c>
-      <c r="O33">
+        <v>18</v>
+      </c>
+      <c r="O33" t="s">
+        <v>18</v>
+      </c>
+      <c r="P33">
         <v>3.945</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:16">
       <c r="A34">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J34" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N34" t="s">
-        <v>17</v>
-      </c>
-      <c r="O34">
+        <v>18</v>
+      </c>
+      <c r="O34" t="s">
+        <v>18</v>
+      </c>
+      <c r="P34">
         <v>3.945</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:16">
       <c r="A35">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K35" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N35" t="s">
-        <v>17</v>
-      </c>
-      <c r="O35">
+        <v>18</v>
+      </c>
+      <c r="O35" t="s">
+        <v>18</v>
+      </c>
+      <c r="P35">
         <v>3.945</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:16">
       <c r="A36">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J36" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N36" t="s">
-        <v>17</v>
-      </c>
-      <c r="O36">
+        <v>18</v>
+      </c>
+      <c r="O36" t="s">
+        <v>18</v>
+      </c>
+      <c r="P36">
         <v>3.945</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:16">
       <c r="A37">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N37" t="s">
-        <v>17</v>
-      </c>
-      <c r="O37">
+        <v>18</v>
+      </c>
+      <c r="O37" t="s">
+        <v>18</v>
+      </c>
+      <c r="P37">
         <v>3.945</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:16">
       <c r="A38">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J38" t="s">
         <v>17</v>
       </c>
       <c r="K38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N38" t="s">
-        <v>17</v>
-      </c>
-      <c r="O38">
+        <v>18</v>
+      </c>
+      <c r="O38" t="s">
+        <v>18</v>
+      </c>
+      <c r="P38">
         <v>3.945</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:16">
       <c r="A39">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N39" t="s">
-        <v>17</v>
-      </c>
-      <c r="O39">
+        <v>18</v>
+      </c>
+      <c r="O39" t="s">
+        <v>18</v>
+      </c>
+      <c r="P39">
         <v>3.945</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:16">
       <c r="A40">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M40" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N40" t="s">
-        <v>17</v>
-      </c>
-      <c r="O40">
+        <v>20</v>
+      </c>
+      <c r="O40" t="s">
+        <v>18</v>
+      </c>
+      <c r="P40">
         <v>3.945</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:16">
       <c r="A41">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N41" t="s">
-        <v>17</v>
-      </c>
-      <c r="O41">
-        <v>3.945</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O41" t="s">
+        <v>60</v>
+      </c>
+      <c r="P41">
+        <v>3.941</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
         <v>17</v>
       </c>
       <c r="J42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N42" t="s">
-        <v>17</v>
-      </c>
-      <c r="O42">
-        <v>3.945</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O42" t="s">
+        <v>43</v>
+      </c>
+      <c r="P42">
+        <v>3.925</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G43" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H43" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J43" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N43" t="s">
-        <v>17</v>
-      </c>
-      <c r="O43">
-        <v>3.945</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O43" t="s">
+        <v>18</v>
+      </c>
+      <c r="P43">
+        <v>3.925</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K44" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N44" t="s">
-        <v>17</v>
-      </c>
-      <c r="O44">
-        <v>3.945</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O44" t="s">
+        <v>18</v>
+      </c>
+      <c r="P44">
+        <v>3.925</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F45" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N45" t="s">
-        <v>19</v>
-      </c>
-      <c r="O45">
-        <v>3.945</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O45" t="s">
+        <v>18</v>
+      </c>
+      <c r="P45">
+        <v>3.925</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C46" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="H46" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M46" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N46" t="s">
         <v>17</v>
       </c>
-      <c r="O46">
-        <v>3.925</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="O46" t="s">
+        <v>18</v>
+      </c>
+      <c r="P46">
+        <v>3.918</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J47" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K47" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="L47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M47" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N47" t="s">
         <v>17</v>
       </c>
-      <c r="O47">
-        <v>3.925</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="O47" t="s">
+        <v>18</v>
+      </c>
+      <c r="P47">
+        <v>3.904</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F48" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K48" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="L48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M48" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>17</v>
-      </c>
-      <c r="O48">
-        <v>3.925</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O48" t="s">
+        <v>18</v>
+      </c>
+      <c r="P48">
+        <v>3.904</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D49" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F49" t="s">
         <v>17</v>
       </c>
       <c r="G49" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L49" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N49" t="s">
-        <v>16</v>
-      </c>
-      <c r="O49">
-        <v>3.918</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O49" t="s">
+        <v>60</v>
+      </c>
+      <c r="P49">
+        <v>3.891</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
       <c r="A50">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E50" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F50" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J50" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K50" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="L50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N50" t="s">
-        <v>16</v>
-      </c>
-      <c r="O50">
-        <v>3.904</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O50" t="s">
+        <v>18</v>
+      </c>
+      <c r="P50">
+        <v>3.891</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
       <c r="A51">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K51" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="L51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M51" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N51" t="s">
-        <v>17</v>
-      </c>
-      <c r="O51">
-        <v>3.904</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O51" t="s">
+        <v>18</v>
+      </c>
+      <c r="P51">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D52" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G52" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M52" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N52" t="s">
-        <v>17</v>
-      </c>
-      <c r="O52">
-        <v>3.891</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O52" t="s">
+        <v>18</v>
+      </c>
+      <c r="P52">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D53" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H53" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N53" t="s">
-        <v>17</v>
-      </c>
-      <c r="O53">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O53" t="s">
+        <v>20</v>
+      </c>
+      <c r="P53">
+        <v>3.873</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D54" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J54" t="s">
         <v>17</v>
       </c>
       <c r="K54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N54" t="s">
-        <v>17</v>
-      </c>
-      <c r="O54">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O54" t="s">
+        <v>18</v>
+      </c>
+      <c r="P54">
+        <v>3.872</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C55" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E55" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F55" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J55" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N55" t="s">
-        <v>17</v>
-      </c>
-      <c r="O55">
+        <v>18</v>
+      </c>
+      <c r="O55" t="s">
+        <v>18</v>
+      </c>
+      <c r="P55">
         <v>3.872</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:16">
       <c r="A56">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="D56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J56" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L56" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M56" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N56" t="s">
-        <v>17</v>
-      </c>
-      <c r="O56">
-        <v>3.872</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O56" t="s">
+        <v>76</v>
+      </c>
+      <c r="P56">
+        <v>3.866</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E57" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F57" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K57" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N57" t="s">
-        <v>17</v>
-      </c>
-      <c r="O57">
+        <v>18</v>
+      </c>
+      <c r="O57" t="s">
+        <v>18</v>
+      </c>
+      <c r="P57">
         <v>3.863</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:16">
       <c r="A58">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I58" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="J58" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K58" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="L58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N58" t="s">
-        <v>17</v>
-      </c>
-      <c r="O58">
-        <v>3.863</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O58" t="s">
+        <v>18</v>
+      </c>
+      <c r="P58">
+        <v>3.862</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J59" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="K59" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="L59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N59" t="s">
-        <v>17</v>
-      </c>
-      <c r="O59">
-        <v>3.862</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O59" t="s">
+        <v>18</v>
+      </c>
+      <c r="P59">
+        <v>3.849</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C60" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E60" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F60" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G60" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J60" t="s">
         <v>17</v>
       </c>
       <c r="K60" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L60" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M60" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N60" t="s">
-        <v>17</v>
-      </c>
-      <c r="O60">
-        <v>3.862</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O60" t="s">
+        <v>81</v>
+      </c>
+      <c r="P60">
+        <v>3.841</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C61" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D61" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E61" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F61" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G61" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H61" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I61" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K61" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N61" t="s">
-        <v>17</v>
-      </c>
-      <c r="O61">
-        <v>3.849</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O61" t="s">
+        <v>18</v>
+      </c>
+      <c r="P61">
+        <v>3.837</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62">
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C62" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J62" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K62" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N62" t="s">
-        <v>17</v>
-      </c>
-      <c r="O62">
-        <v>3.849</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O62" t="s">
+        <v>18</v>
+      </c>
+      <c r="P62">
+        <v>3.837</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C63" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E63" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F63" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G63" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K63" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="L63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M63" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="N63" t="s">
         <v>17</v>
       </c>
-      <c r="O63">
-        <v>3.837</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15">
+      <c r="O63" t="s">
+        <v>18</v>
+      </c>
+      <c r="P63">
+        <v>3.822</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
       <c r="A64">
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C64" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E64" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G64" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H64" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="J64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K64" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="L64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M64" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N64" t="s">
-        <v>17</v>
-      </c>
-      <c r="O64">
-        <v>3.837</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15">
+        <v>20</v>
+      </c>
+      <c r="O64" t="s">
+        <v>18</v>
+      </c>
+      <c r="P64">
+        <v>3.822</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D65" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E65" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G65" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K65" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N65" t="s">
-        <v>17</v>
-      </c>
-      <c r="O65">
-        <v>3.833</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O65" t="s">
+        <v>18</v>
+      </c>
+      <c r="P65">
+        <v>3.818</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
       <c r="A66">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E66" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F66" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="J66" t="s">
         <v>17</v>
       </c>
       <c r="K66" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="L66" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M66" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="N66" t="s">
-        <v>16</v>
-      </c>
-      <c r="O66">
-        <v>3.822</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O66" t="s">
+        <v>18</v>
+      </c>
+      <c r="P66">
+        <v>3.818</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
       <c r="A67">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="D67" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F67" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="J67" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K67" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="L67" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N67" t="s">
-        <v>19</v>
-      </c>
-      <c r="O67">
-        <v>3.822</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O67" t="s">
+        <v>18</v>
+      </c>
+      <c r="P67">
+        <v>3.818</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C68" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="D68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F68" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K68" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="L68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N68" t="s">
-        <v>17</v>
-      </c>
-      <c r="O68">
-        <v>3.818</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O68" t="s">
+        <v>60</v>
+      </c>
+      <c r="P68">
+        <v>3.816</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
       <c r="A69">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C69" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" t="s">
+        <v>43</v>
+      </c>
+      <c r="E69" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>17</v>
+      </c>
+      <c r="H69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I69" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" t="s">
+        <v>76</v>
+      </c>
+      <c r="L69" t="s">
+        <v>18</v>
+      </c>
+      <c r="M69" t="s">
+        <v>20</v>
+      </c>
+      <c r="N69" t="s">
+        <v>17</v>
+      </c>
+      <c r="O69" t="s">
+        <v>18</v>
+      </c>
+      <c r="P69">
+        <v>3.809</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70">
         <v>68</v>
       </c>
-      <c r="D69" t="s">
-        <v>44</v>
-      </c>
-      <c r="E69" t="s">
-        <v>19</v>
-      </c>
-      <c r="F69" t="s">
-        <v>19</v>
-      </c>
-      <c r="G69" t="s">
-        <v>16</v>
-      </c>
-      <c r="H69" t="s">
-        <v>17</v>
-      </c>
-      <c r="I69" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" t="s">
-        <v>16</v>
-      </c>
-      <c r="K69" t="s">
-        <v>19</v>
-      </c>
-      <c r="L69" t="s">
-        <v>17</v>
-      </c>
-      <c r="M69" t="s">
-        <v>17</v>
-      </c>
-      <c r="N69" t="s">
-        <v>17</v>
-      </c>
-      <c r="O69">
-        <v>3.818</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15">
-      <c r="A70">
-        <v>67</v>
-      </c>
       <c r="B70" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="D70" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E70" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F70" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G70" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K70" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="L70" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M70" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N70" t="s">
-        <v>17</v>
-      </c>
-      <c r="O70">
-        <v>3.818</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O70" t="s">
+        <v>18</v>
+      </c>
+      <c r="P70">
+        <v>3.809</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C71" t="s">
         <v>17</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="F71" t="s">
         <v>17</v>
       </c>
       <c r="G71" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H71" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I71" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K71" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="L71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N71" t="s">
-        <v>16</v>
-      </c>
-      <c r="O71">
-        <v>3.809</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O71" t="s">
+        <v>18</v>
+      </c>
+      <c r="P71">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
       <c r="A72">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C72" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D72" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E72" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F72" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G72" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H72" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I72" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K72" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="L72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M72" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N72" t="s">
-        <v>17</v>
-      </c>
-      <c r="O72">
-        <v>3.809</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O72" t="s">
+        <v>18</v>
+      </c>
+      <c r="P72">
+        <v>3.799</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D73" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E73" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H73" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J73" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="K73" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="L73" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="M73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N73" t="s">
-        <v>17</v>
-      </c>
-      <c r="O73">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O73" t="s">
+        <v>18</v>
+      </c>
+      <c r="P73">
+        <v>3.796</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C74" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F74" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G74" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H74" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I74" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="J74" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="K74" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="L74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M74" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N74" t="s">
-        <v>17</v>
-      </c>
-      <c r="O74">
-        <v>3.799</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O74" t="s">
+        <v>18</v>
+      </c>
+      <c r="P74">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C75" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D75" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J75" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="K75" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L75" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="M75" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N75" t="s">
-        <v>17</v>
-      </c>
-      <c r="O75">
-        <v>3.796</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O75" t="s">
+        <v>76</v>
+      </c>
+      <c r="P75">
+        <v>3.779</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D76" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E76" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F76" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H76" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J76" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="K76" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="L76" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M76" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N76" t="s">
-        <v>17</v>
-      </c>
-      <c r="O76">
-        <v>3.79</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O76" t="s">
+        <v>18</v>
+      </c>
+      <c r="P76">
+        <v>3.777</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C77" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F77" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G77" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H77" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J77" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K77" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L77" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M77" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N77" t="s">
-        <v>17</v>
-      </c>
-      <c r="O77">
+        <v>18</v>
+      </c>
+      <c r="O77" t="s">
+        <v>18</v>
+      </c>
+      <c r="P77">
         <v>3.775</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:16">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C78" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D78" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E78" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F78" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G78" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H78" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I78" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="J78" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K78" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L78" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N78" t="s">
-        <v>16</v>
-      </c>
-      <c r="O78">
-        <v>3.768</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O78" t="s">
+        <v>18</v>
+      </c>
+      <c r="P78">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C79" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="D79" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G79" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H79" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="J79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K79" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="L79" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M79" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N79" t="s">
         <v>17</v>
       </c>
-      <c r="O79">
+      <c r="O79" t="s">
+        <v>18</v>
+      </c>
+      <c r="P79">
+        <v>3.768</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>101</v>
+      </c>
+      <c r="C80" t="s">
+        <v>76</v>
+      </c>
+      <c r="D80" t="s">
+        <v>43</v>
+      </c>
+      <c r="E80" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" t="s">
+        <v>17</v>
+      </c>
+      <c r="H80" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" t="s">
+        <v>18</v>
+      </c>
+      <c r="J80" t="s">
+        <v>20</v>
+      </c>
+      <c r="K80" t="s">
+        <v>17</v>
+      </c>
+      <c r="L80" t="s">
+        <v>18</v>
+      </c>
+      <c r="M80" t="s">
+        <v>18</v>
+      </c>
+      <c r="N80" t="s">
+        <v>18</v>
+      </c>
+      <c r="O80" t="s">
+        <v>18</v>
+      </c>
+      <c r="P80">
         <v>3.763</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
-      <c r="A80">
-        <v>78</v>
-      </c>
-      <c r="B80" t="s">
-        <v>99</v>
-      </c>
-      <c r="C80" t="s">
-        <v>100</v>
-      </c>
-      <c r="D80" t="s">
-        <v>19</v>
-      </c>
-      <c r="E80" t="s">
-        <v>19</v>
-      </c>
-      <c r="F80" t="s">
-        <v>16</v>
-      </c>
-      <c r="G80" t="s">
-        <v>19</v>
-      </c>
-      <c r="H80" t="s">
-        <v>17</v>
-      </c>
-      <c r="I80" t="s">
-        <v>19</v>
-      </c>
-      <c r="J80" t="s">
-        <v>17</v>
-      </c>
-      <c r="K80" t="s">
-        <v>19</v>
-      </c>
-      <c r="L80" t="s">
-        <v>17</v>
-      </c>
-      <c r="M80" t="s">
-        <v>17</v>
-      </c>
-      <c r="N80" t="s">
-        <v>17</v>
-      </c>
-      <c r="O80">
+    <row r="81" spans="1:16">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81" t="s">
+        <v>102</v>
+      </c>
+      <c r="C81" t="s">
+        <v>81</v>
+      </c>
+      <c r="D81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" t="s">
+        <v>17</v>
+      </c>
+      <c r="G81" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" t="s">
+        <v>18</v>
+      </c>
+      <c r="K81" t="s">
+        <v>20</v>
+      </c>
+      <c r="L81" t="s">
+        <v>18</v>
+      </c>
+      <c r="M81" t="s">
+        <v>18</v>
+      </c>
+      <c r="N81" t="s">
+        <v>18</v>
+      </c>
+      <c r="O81" t="s">
+        <v>18</v>
+      </c>
+      <c r="P81">
         <v>3.763</v>
       </c>
     </row>
-    <row r="81" spans="1:15">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="s">
-        <v>101</v>
-      </c>
-      <c r="C81" t="s">
-        <v>68</v>
-      </c>
-      <c r="D81" t="s">
-        <v>44</v>
-      </c>
-      <c r="E81" t="s">
-        <v>19</v>
-      </c>
-      <c r="F81" t="s">
-        <v>19</v>
-      </c>
-      <c r="G81" t="s">
-        <v>16</v>
-      </c>
-      <c r="H81" t="s">
-        <v>16</v>
-      </c>
-      <c r="I81" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" t="s">
-        <v>44</v>
-      </c>
-      <c r="K81" t="s">
-        <v>44</v>
-      </c>
-      <c r="L81" t="s">
-        <v>17</v>
-      </c>
-      <c r="M81" t="s">
-        <v>17</v>
-      </c>
-      <c r="N81" t="s">
-        <v>17</v>
-      </c>
-      <c r="O81">
-        <v>3.758</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:16">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C82" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D82" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="E82" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F82" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G82" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H82" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J82" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="K82" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="L82" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M82" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N82" t="s">
-        <v>17</v>
-      </c>
-      <c r="O82">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O82" t="s">
+        <v>18</v>
+      </c>
+      <c r="P82">
+        <v>3.758</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C83" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="D83" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E83" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F83" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H83" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="I83" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J83" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K83" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L83" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M83" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N83" t="s">
-        <v>17</v>
-      </c>
-      <c r="O83">
-        <v>3.745</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O83" t="s">
+        <v>18</v>
+      </c>
+      <c r="P83">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
       <c r="A84">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C84" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D84" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E84" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G84" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H84" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I84" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="J84" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K84" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L84" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M84" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N84" t="s">
-        <v>17</v>
-      </c>
-      <c r="O84">
-        <v>3.745</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O84" t="s">
+        <v>81</v>
+      </c>
+      <c r="P84">
+        <v>3.746</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C85" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D85" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E85" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F85" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G85" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H85" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I85" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J85" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K85" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L85" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M85" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N85" t="s">
-        <v>17</v>
-      </c>
-      <c r="O85">
-        <v>3.741</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O85" t="s">
+        <v>18</v>
+      </c>
+      <c r="P85">
+        <v>3.745</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
       <c r="A86">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C86" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D86" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E86" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F86" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G86" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H86" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="J86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K86" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N86" t="s">
-        <v>17</v>
-      </c>
-      <c r="O86">
-        <v>3.736</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O86" t="s">
+        <v>18</v>
+      </c>
+      <c r="P86">
+        <v>3.745</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C87" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D87" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F87" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G87" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H87" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I87" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="J87" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K87" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L87" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M87" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N87" t="s">
-        <v>17</v>
-      </c>
-      <c r="O87">
-        <v>3.722</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O87" t="s">
+        <v>18</v>
+      </c>
+      <c r="P87">
+        <v>3.741</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
       <c r="A88">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C88" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E88" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F88" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G88" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K88" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="L88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M88" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N88" t="s">
-        <v>17</v>
-      </c>
-      <c r="O88">
-        <v>3.722</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O88" t="s">
+        <v>18</v>
+      </c>
+      <c r="P88">
+        <v>3.736</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C89" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D89" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="E89" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F89" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G89" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H89" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="J89" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K89" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L89" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M89" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N89" t="s">
-        <v>17</v>
-      </c>
-      <c r="O89">
+        <v>18</v>
+      </c>
+      <c r="O89" t="s">
+        <v>18</v>
+      </c>
+      <c r="P89">
+        <v>3.722</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>111</v>
+      </c>
+      <c r="C90" t="s">
+        <v>60</v>
+      </c>
+      <c r="D90" t="s">
+        <v>76</v>
+      </c>
+      <c r="E90" t="s">
+        <v>20</v>
+      </c>
+      <c r="F90" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" t="s">
+        <v>17</v>
+      </c>
+      <c r="I90" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" t="s">
+        <v>17</v>
+      </c>
+      <c r="K90" t="s">
+        <v>20</v>
+      </c>
+      <c r="L90" t="s">
+        <v>18</v>
+      </c>
+      <c r="M90" t="s">
+        <v>18</v>
+      </c>
+      <c r="N90" t="s">
+        <v>18</v>
+      </c>
+      <c r="O90" t="s">
+        <v>18</v>
+      </c>
+      <c r="P90">
         <v>3.716</v>
       </c>
     </row>
-    <row r="90" spans="1:15">
-      <c r="A90">
-        <v>88</v>
-      </c>
-      <c r="B90" t="s">
-        <v>110</v>
-      </c>
-      <c r="C90" t="s">
-        <v>68</v>
-      </c>
-      <c r="D90" t="s">
-        <v>84</v>
-      </c>
-      <c r="E90" t="s">
-        <v>19</v>
-      </c>
-      <c r="F90" t="s">
-        <v>16</v>
-      </c>
-      <c r="G90" t="s">
-        <v>16</v>
-      </c>
-      <c r="H90" t="s">
-        <v>19</v>
-      </c>
-      <c r="I90" t="s">
-        <v>19</v>
-      </c>
-      <c r="J90" t="s">
-        <v>17</v>
-      </c>
-      <c r="K90" t="s">
-        <v>19</v>
-      </c>
-      <c r="L90" t="s">
-        <v>17</v>
-      </c>
-      <c r="M90" t="s">
-        <v>17</v>
-      </c>
-      <c r="N90" t="s">
-        <v>17</v>
-      </c>
-      <c r="O90">
+    <row r="91" spans="1:16">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91" t="s">
+        <v>112</v>
+      </c>
+      <c r="C91" t="s">
+        <v>60</v>
+      </c>
+      <c r="D91" t="s">
+        <v>76</v>
+      </c>
+      <c r="E91" t="s">
+        <v>20</v>
+      </c>
+      <c r="F91" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" t="s">
+        <v>17</v>
+      </c>
+      <c r="H91" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" t="s">
+        <v>20</v>
+      </c>
+      <c r="J91" t="s">
+        <v>18</v>
+      </c>
+      <c r="K91" t="s">
+        <v>20</v>
+      </c>
+      <c r="L91" t="s">
+        <v>18</v>
+      </c>
+      <c r="M91" t="s">
+        <v>18</v>
+      </c>
+      <c r="N91" t="s">
+        <v>18</v>
+      </c>
+      <c r="O91" t="s">
+        <v>18</v>
+      </c>
+      <c r="P91">
         <v>3.716</v>
       </c>
     </row>
-    <row r="91" spans="1:15">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="s">
-        <v>111</v>
-      </c>
-      <c r="C91" t="s">
-        <v>68</v>
-      </c>
-      <c r="D91" t="s">
-        <v>68</v>
-      </c>
-      <c r="E91" t="s">
-        <v>19</v>
-      </c>
-      <c r="F91" t="s">
-        <v>19</v>
-      </c>
-      <c r="G91" t="s">
-        <v>16</v>
-      </c>
-      <c r="H91" t="s">
-        <v>44</v>
-      </c>
-      <c r="I91" t="s">
-        <v>17</v>
-      </c>
-      <c r="J91" t="s">
-        <v>19</v>
-      </c>
-      <c r="K91" t="s">
-        <v>44</v>
-      </c>
-      <c r="L91" t="s">
-        <v>17</v>
-      </c>
-      <c r="M91" t="s">
-        <v>17</v>
-      </c>
-      <c r="N91" t="s">
-        <v>17</v>
-      </c>
-      <c r="O91">
-        <v>3.704</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15">
+    <row r="92" spans="1:16">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C92" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D92" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E92" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F92" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G92" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="J92" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K92" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L92" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N92" t="s">
-        <v>16</v>
-      </c>
-      <c r="O92">
-        <v>3.695</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O92" t="s">
+        <v>20</v>
+      </c>
+      <c r="P92">
+        <v>3.708</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C93" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D93" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E93" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F93" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G93" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K93" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L93" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M93" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N93" t="s">
         <v>17</v>
       </c>
-      <c r="O93">
-        <v>3.681</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15">
+      <c r="O93" t="s">
+        <v>18</v>
+      </c>
+      <c r="P93">
+        <v>3.695</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C94" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D94" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F94" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G94" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H94" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I94" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="J94" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K94" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="L94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M94" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N94" t="s">
-        <v>17</v>
-      </c>
-      <c r="O94">
+        <v>18</v>
+      </c>
+      <c r="O94" t="s">
+        <v>43</v>
+      </c>
+      <c r="P94">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>116</v>
+      </c>
+      <c r="C95" t="s">
+        <v>76</v>
+      </c>
+      <c r="D95" t="s">
+        <v>60</v>
+      </c>
+      <c r="E95" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" t="s">
+        <v>17</v>
+      </c>
+      <c r="H95" t="s">
+        <v>20</v>
+      </c>
+      <c r="I95" t="s">
+        <v>43</v>
+      </c>
+      <c r="J95" t="s">
+        <v>18</v>
+      </c>
+      <c r="K95" t="s">
+        <v>20</v>
+      </c>
+      <c r="L95" t="s">
+        <v>18</v>
+      </c>
+      <c r="M95" t="s">
+        <v>18</v>
+      </c>
+      <c r="N95" t="s">
+        <v>18</v>
+      </c>
+      <c r="O95" t="s">
+        <v>18</v>
+      </c>
+      <c r="P95">
         <v>3.679</v>
       </c>
     </row>
-    <row r="95" spans="1:15">
-      <c r="A95">
-        <v>93</v>
-      </c>
-      <c r="B95" t="s">
-        <v>115</v>
-      </c>
-      <c r="C95" t="s">
-        <v>84</v>
-      </c>
-      <c r="D95" t="s">
-        <v>68</v>
-      </c>
-      <c r="E95" t="s">
-        <v>19</v>
-      </c>
-      <c r="F95" t="s">
-        <v>16</v>
-      </c>
-      <c r="G95" t="s">
-        <v>16</v>
-      </c>
-      <c r="H95" t="s">
-        <v>19</v>
-      </c>
-      <c r="I95" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" t="s">
-        <v>19</v>
-      </c>
-      <c r="K95" t="s">
-        <v>44</v>
-      </c>
-      <c r="L95" t="s">
-        <v>17</v>
-      </c>
-      <c r="M95" t="s">
-        <v>17</v>
-      </c>
-      <c r="N95" t="s">
-        <v>17</v>
-      </c>
-      <c r="O95">
+    <row r="96" spans="1:16">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96" t="s">
+        <v>117</v>
+      </c>
+      <c r="C96" t="s">
+        <v>76</v>
+      </c>
+      <c r="D96" t="s">
+        <v>60</v>
+      </c>
+      <c r="E96" t="s">
+        <v>20</v>
+      </c>
+      <c r="F96" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" t="s">
+        <v>20</v>
+      </c>
+      <c r="H96" t="s">
+        <v>20</v>
+      </c>
+      <c r="I96" t="s">
+        <v>20</v>
+      </c>
+      <c r="J96" t="s">
+        <v>18</v>
+      </c>
+      <c r="K96" t="s">
+        <v>43</v>
+      </c>
+      <c r="L96" t="s">
+        <v>18</v>
+      </c>
+      <c r="M96" t="s">
+        <v>18</v>
+      </c>
+      <c r="N96" t="s">
+        <v>18</v>
+      </c>
+      <c r="O96" t="s">
+        <v>18</v>
+      </c>
+      <c r="P96">
         <v>3.679</v>
       </c>
     </row>
-    <row r="96" spans="1:15">
-      <c r="A96">
-        <v>93</v>
-      </c>
-      <c r="B96" t="s">
-        <v>116</v>
-      </c>
-      <c r="C96" t="s">
-        <v>84</v>
-      </c>
-      <c r="D96" t="s">
-        <v>68</v>
-      </c>
-      <c r="E96" t="s">
-        <v>19</v>
-      </c>
-      <c r="F96" t="s">
-        <v>16</v>
-      </c>
-      <c r="G96" t="s">
-        <v>19</v>
-      </c>
-      <c r="H96" t="s">
-        <v>19</v>
-      </c>
-      <c r="I96" t="s">
-        <v>19</v>
-      </c>
-      <c r="J96" t="s">
-        <v>17</v>
-      </c>
-      <c r="K96" t="s">
-        <v>44</v>
-      </c>
-      <c r="L96" t="s">
-        <v>17</v>
-      </c>
-      <c r="M96" t="s">
-        <v>17</v>
-      </c>
-      <c r="N96" t="s">
-        <v>17</v>
-      </c>
-      <c r="O96">
-        <v>3.679</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15">
+    <row r="97" spans="1:16">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C97" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D97" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E97" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F97" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G97" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J97" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K97" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M97" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N97" t="s">
-        <v>17</v>
-      </c>
-      <c r="O97">
+        <v>18</v>
+      </c>
+      <c r="O97" t="s">
+        <v>18</v>
+      </c>
+      <c r="P97">
         <v>3.654</v>
       </c>
     </row>
-    <row r="98" spans="1:15">
+    <row r="98" spans="1:16">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C98" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D98" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E98" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G98" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N98" t="s">
-        <v>17</v>
-      </c>
-      <c r="O98">
+        <v>18</v>
+      </c>
+      <c r="O98" t="s">
+        <v>18</v>
+      </c>
+      <c r="P98">
         <v>3.65</v>
       </c>
     </row>
-    <row r="99" spans="1:15">
+    <row r="99" spans="1:16">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C99" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D99" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E99" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="F99" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G99" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H99" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I99" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="J99" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K99" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="L99" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M99" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N99" t="s">
-        <v>17</v>
-      </c>
-      <c r="O99">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O99" t="s">
+        <v>43</v>
+      </c>
+      <c r="P99">
+        <v>3.645</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
       <c r="A100">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C100" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="D100" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E100" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F100" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G100" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H100" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="J100" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K100" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L100" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M100" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N100" t="s">
-        <v>17</v>
-      </c>
-      <c r="O100">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O100" t="s">
+        <v>43</v>
+      </c>
+      <c r="P100">
+        <v>3.641</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C101" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="D101" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E101" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F101" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G101" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H101" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J101" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K101" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="L101" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M101" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N101" t="s">
-        <v>17</v>
-      </c>
-      <c r="O101">
-        <v>3.636</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O101" t="s">
+        <v>18</v>
+      </c>
+      <c r="P101">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C102" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D102" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E102" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F102" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G102" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H102" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I102" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J102" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K102" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L102" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M102" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N102" t="s">
-        <v>17</v>
-      </c>
-      <c r="O102">
+        <v>18</v>
+      </c>
+      <c r="O102" t="s">
+        <v>18</v>
+      </c>
+      <c r="P102">
         <v>3.629</v>
       </c>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:16">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C103" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D103" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E103" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F103" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G103" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H103" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I103" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J103" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K103" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L103" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M103" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N103" t="s">
-        <v>17</v>
-      </c>
-      <c r="O103">
-        <v>3.627</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O103" t="s">
+        <v>60</v>
+      </c>
+      <c r="P103">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C104" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D104" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E104" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F104" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G104" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H104" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I104" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J104" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K104" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L104" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M104" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N104" t="s">
-        <v>17</v>
-      </c>
-      <c r="O104">
+        <v>18</v>
+      </c>
+      <c r="O104" t="s">
+        <v>18</v>
+      </c>
+      <c r="P104">
         <v>3.513</v>
       </c>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:16">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D105" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E105" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F105" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G105" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H105" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I105" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J105" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K105" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L105" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M105" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="N105" t="s">
-        <v>19</v>
-      </c>
-      <c r="O105">
+        <v>20</v>
+      </c>
+      <c r="O105" t="s">
+        <v>18</v>
+      </c>
+      <c r="P105">
         <v>3.49</v>
       </c>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:16">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D106" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="E106" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G106" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I106" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K106" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L106" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M106" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N106" t="s">
-        <v>16</v>
-      </c>
-      <c r="O106">
+        <v>17</v>
+      </c>
+      <c r="O106" t="s">
+        <v>18</v>
+      </c>
+      <c r="P106">
         <v>3.468</v>
       </c>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:16">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C107" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D107" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E107" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F107" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G107" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H107" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I107" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J107" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K107" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L107" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="M107" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N107" t="s">
-        <v>17</v>
-      </c>
-      <c r="O107">
+        <v>18</v>
+      </c>
+      <c r="O107" t="s">
+        <v>18</v>
+      </c>
+      <c r="P107">
         <v>3.452</v>
       </c>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:16">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C108" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D108" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="E108" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F108" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G108" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H108" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J108" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K108" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L108" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M108" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N108" t="s">
-        <v>17</v>
-      </c>
-      <c r="O108">
+        <v>18</v>
+      </c>
+      <c r="O108" t="s">
+        <v>18</v>
+      </c>
+      <c r="P108">
         <v>3.445</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:16">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C109" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="D109" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E109" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="F109" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G109" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H109" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I109" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J109" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K109" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="L109" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M109" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N109" t="s">
-        <v>17</v>
-      </c>
-      <c r="O109">
-        <v>3.427</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O109" t="s">
+        <v>18</v>
+      </c>
+      <c r="P109">
+        <v>3.404</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6643,324 +7036,345 @@
         <v>131</v>
       </c>
       <c r="C110" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="D110" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="E110" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="F110" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G110" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K110" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="L110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N110" t="s">
-        <v>17</v>
-      </c>
-      <c r="O110">
-        <v>3.404</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15">
+        <v>18</v>
+      </c>
+      <c r="O110" t="s">
+        <v>132</v>
+      </c>
+      <c r="P110">
+        <v>3.333</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D111" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E111" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G111" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J111" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K111" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M111" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N111" t="s">
-        <v>16</v>
-      </c>
-      <c r="O111">
+        <v>17</v>
+      </c>
+      <c r="O111" t="s">
+        <v>18</v>
+      </c>
+      <c r="P111">
         <v>3.19</v>
       </c>
     </row>
-    <row r="112" spans="1:15">
+    <row r="112" spans="1:16">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" t="s">
+        <v>135</v>
+      </c>
+      <c r="C112" t="s">
+        <v>76</v>
+      </c>
+      <c r="D112" t="s">
         <v>134</v>
       </c>
-      <c r="C112" t="s">
-        <v>84</v>
-      </c>
-      <c r="D112" t="s">
-        <v>133</v>
-      </c>
       <c r="E112" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F112" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G112" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H112" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K112" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N112" t="s">
-        <v>17</v>
-      </c>
-      <c r="O112">
+        <v>18</v>
+      </c>
+      <c r="O112" t="s">
+        <v>18</v>
+      </c>
+      <c r="P112">
         <v>3.054</v>
       </c>
     </row>
-    <row r="113" spans="1:15">
+    <row r="113" spans="1:16">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D113" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E113" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F113" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G113" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H113" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I113" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J113" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K113" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L113" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M113" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N113" t="s">
-        <v>17</v>
-      </c>
-      <c r="O113">
+        <v>18</v>
+      </c>
+      <c r="O113" t="s">
+        <v>18</v>
+      </c>
+      <c r="P113">
         <v>3.029</v>
       </c>
     </row>
-    <row r="114" spans="1:15">
+    <row r="114" spans="1:16">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D114" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E114" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F114" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G114" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H114" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J114" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K114" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L114" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M114" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N114" t="s">
-        <v>17</v>
-      </c>
-      <c r="O114">
+        <v>18</v>
+      </c>
+      <c r="O114" t="s">
+        <v>18</v>
+      </c>
+      <c r="P114">
         <v>3.009</v>
       </c>
     </row>
-    <row r="115" spans="1:15">
+    <row r="115" spans="1:16">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D115" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="E115" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F115" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G115" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H115" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I115" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J115" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K115" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="L115" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M115" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N115" t="s">
-        <v>17</v>
-      </c>
-      <c r="O115">
+        <v>18</v>
+      </c>
+      <c r="O115" t="s">
+        <v>18</v>
+      </c>
+      <c r="P115">
         <v>2.954</v>
       </c>
     </row>
-    <row r="116" spans="1:15">
+    <row r="116" spans="1:16">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D116" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E116" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F116" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="G116" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H116" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="J116" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K116" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L116" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M116" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N116" t="s">
-        <v>17</v>
-      </c>
-      <c r="O116">
+        <v>18</v>
+      </c>
+      <c r="O116" t="s">
+        <v>18</v>
+      </c>
+      <c r="P116">
         <v>1.827</v>
       </c>
     </row>
